--- a/data/trans_orig/IP07A18-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A18-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que se riesen de él/ella otros chicos en 2007 (tasa de respuesta: 99,1%)</t>
+          <t>Menores según la frecuencia de que se riesen de él/ella otros/as chicos/as, percibida por el adulto en 2007 (tasa de respuesta: 99,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2933</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10532</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>10435</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6981</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16931</t>
+          <t>17180</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3676</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11204</t>
+          <t>11883</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2067</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9361</t>
+          <t>9864</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18770</t>
+          <t>18068</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15013</t>
+          <t>15023</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10581</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10053</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22353</t>
+          <t>21848</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>11660</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24407</t>
+          <t>24464</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>15568</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29858</t>
+          <t>30553</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31124</t>
+          <t>29936</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50441</t>
+          <t>47861</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77374</t>
+          <t>78317</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93918</t>
+          <t>94036</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>92799</t>
+          <t>92549</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>109854</t>
+          <t>109515</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>174911</t>
+          <t>176923</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>199600</t>
+          <t>199719</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,18%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>7196</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12204</t>
+          <t>12265</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15704</t>
+          <t>15549</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10980</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12132</t>
+          <t>12126</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8088</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19643</t>
+          <t>20290</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11820</t>
+          <t>12518</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2274</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9542</t>
+          <t>9924</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>7782</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18836</t>
+          <t>18218</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18740</t>
+          <t>18800</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34986</t>
+          <t>34474</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12731</t>
+          <t>12873</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25636</t>
+          <t>25505</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34497</t>
+          <t>34793</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54733</t>
+          <t>54608</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>141186</t>
+          <t>141329</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>161543</t>
+          <t>159548</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>156425</t>
+          <t>157660</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174553</t>
+          <t>175392</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>305391</t>
+          <t>305631</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>330357</t>
+          <t>331286</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,37%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13818</t>
+          <t>13577</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19818</t>
+          <t>19351</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14909</t>
+          <t>15229</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>30015</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8650</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20131</t>
+          <t>20079</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17715</t>
+          <t>18748</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17852</t>
+          <t>18608</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34043</t>
+          <t>33968</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>11393</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24095</t>
+          <t>23644</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>7080</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17356</t>
+          <t>17779</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20602</t>
+          <t>20586</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>37252</t>
+          <t>38001</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34237</t>
+          <t>33604</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53543</t>
+          <t>52873</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31149</t>
+          <t>31399</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50721</t>
+          <t>49887</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>70125</t>
+          <t>70336</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>97621</t>
+          <t>96458</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224753</t>
+          <t>225649</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>250263</t>
+          <t>250763</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>254304</t>
+          <t>256237</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>280096</t>
+          <t>279749</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>490736</t>
+          <t>487335</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>524086</t>
+          <t>523011</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,88%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que se riesen de él/ella otros chicos en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de que se riesen de él/ella otros/as chicos/as, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8749</t>
+          <t>8543</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20686</t>
+          <t>20394</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12103</t>
+          <t>12246</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25229</t>
+          <t>25613</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23448</t>
+          <t>23666</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41600</t>
+          <t>42462</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9763</t>
+          <t>9688</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21719</t>
+          <t>21347</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>7910</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19737</t>
+          <t>19773</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20566</t>
+          <t>20558</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37330</t>
+          <t>35971</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9261</t>
+          <t>9721</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21817</t>
+          <t>21408</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>15523</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29803</t>
+          <t>29589</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27983</t>
+          <t>28525</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46848</t>
+          <t>46663</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11166</t>
+          <t>10897</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23736</t>
+          <t>24469</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15128</t>
+          <t>14158</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28593</t>
+          <t>28291</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28912</t>
+          <t>29067</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47797</t>
+          <t>49095</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85192</t>
+          <t>86009</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>105866</t>
+          <t>104548</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72393</t>
+          <t>72676</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93925</t>
+          <t>92786</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>163409</t>
+          <t>163824</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>193097</t>
+          <t>194753</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>62,38%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>4982</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14862</t>
+          <t>14922</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12152</t>
+          <t>12932</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10873</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23502</t>
+          <t>23382</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11497</t>
+          <t>11248</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24157</t>
+          <t>23888</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11897</t>
+          <t>11809</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24216</t>
+          <t>24015</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25551</t>
+          <t>25603</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43978</t>
+          <t>43133</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6735</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18668</t>
+          <t>19213</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>6160</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16478</t>
+          <t>16154</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15895</t>
+          <t>15295</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30477</t>
+          <t>30358</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14508</t>
+          <t>14950</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28679</t>
+          <t>29195</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9796</t>
+          <t>9612</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21982</t>
+          <t>20933</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26753</t>
+          <t>27437</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45412</t>
+          <t>46189</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97345</t>
+          <t>97539</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>117203</t>
+          <t>117232</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>115179</t>
+          <t>116091</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134465</t>
+          <t>134128</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>218025</t>
+          <t>216347</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>246624</t>
+          <t>245553</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,02%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15659</t>
+          <t>16166</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31052</t>
+          <t>31270</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>17396</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33408</t>
+          <t>33433</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37266</t>
+          <t>38300</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60892</t>
+          <t>59619</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23797</t>
+          <t>23699</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41847</t>
+          <t>41511</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21758</t>
+          <t>23042</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39034</t>
+          <t>39199</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50518</t>
+          <t>49646</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74079</t>
+          <t>74728</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18885</t>
+          <t>18798</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36410</t>
+          <t>35156</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24570</t>
+          <t>24539</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42103</t>
+          <t>42357</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>46722</t>
+          <t>47465</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>71771</t>
+          <t>71949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29423</t>
+          <t>29172</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>48664</t>
+          <t>47843</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27429</t>
+          <t>27728</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45909</t>
+          <t>44694</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60573</t>
+          <t>62134</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>87318</t>
+          <t>88881</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>188028</t>
+          <t>188446</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>216004</t>
+          <t>216084</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>195050</t>
+          <t>194452</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>222932</t>
+          <t>222776</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>388322</t>
+          <t>389522</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>429204</t>
+          <t>430425</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,9%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que se riesen de él/ella otros chicos en 2016 (tasa de respuesta: 98,52%)</t>
+          <t>Menores según la frecuencia de que se riesen de él/ella otros/as chicos/as, percibida por el adulto en 2016 (tasa de respuesta: 98,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2663</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10695</t>
+          <t>11130</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7364</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18760</t>
+          <t>19056</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11843</t>
+          <t>12163</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25677</t>
+          <t>25926</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19628</t>
+          <t>20453</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>5989</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17080</t>
+          <t>17052</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16985</t>
+          <t>16767</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31782</t>
+          <t>32082</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19567</t>
+          <t>20176</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13798</t>
+          <t>14199</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28165</t>
+          <t>28251</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26014</t>
+          <t>25457</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44332</t>
+          <t>43323</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12737</t>
+          <t>12645</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27118</t>
+          <t>26525</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15259</t>
+          <t>15581</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30201</t>
+          <t>30185</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31942</t>
+          <t>31768</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51783</t>
+          <t>51873</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>123827</t>
+          <t>123569</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>143533</t>
+          <t>144372</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>108279</t>
+          <t>108012</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>131512</t>
+          <t>130503</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>238413</t>
+          <t>237960</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>268229</t>
+          <t>267760</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,28%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>3985</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13872</t>
+          <t>13175</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14216</t>
+          <t>15817</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10638</t>
+          <t>10760</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23901</t>
+          <t>24465</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8113</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19639</t>
+          <t>19728</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8618</t>
+          <t>8691</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21653</t>
+          <t>21169</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19841</t>
+          <t>20273</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36604</t>
+          <t>37549</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18253</t>
+          <t>19260</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>7559</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18973</t>
+          <t>19427</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17086</t>
+          <t>17486</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33030</t>
+          <t>33808</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14757</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28940</t>
+          <t>29773</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12523</t>
+          <t>12474</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26346</t>
+          <t>26489</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30833</t>
+          <t>30940</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50937</t>
+          <t>50390</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -6418,12 +6418,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>106374</t>
+          <t>107001</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>127108</t>
+          <t>126185</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,28%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>108144</t>
+          <t>109588</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129084</t>
+          <t>130326</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>220624</t>
+          <t>221508</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>250291</t>
+          <t>250725</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,83%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8627</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21052</t>
+          <t>20649</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14372</t>
+          <t>13792</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29025</t>
+          <t>29863</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25662</t>
+          <t>25172</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45668</t>
+          <t>44834</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18869</t>
+          <t>19291</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35410</t>
+          <t>35048</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17113</t>
+          <t>16873</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33560</t>
+          <t>33309</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40274</t>
+          <t>40707</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63195</t>
+          <t>63790</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18057</t>
+          <t>18676</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34156</t>
+          <t>34537</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24871</t>
+          <t>24689</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43593</t>
+          <t>42366</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>46452</t>
+          <t>48256</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>70706</t>
+          <t>72384</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31016</t>
+          <t>30920</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50507</t>
+          <t>50458</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32343</t>
+          <t>32854</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53084</t>
+          <t>54111</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>68378</t>
+          <t>66607</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>95802</t>
+          <t>94505</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -7100,12 +7100,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236266</t>
+          <t>235151</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264931</t>
+          <t>263536</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>222876</t>
+          <t>223033</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>253116</t>
+          <t>252592</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7150,12 +7150,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>468261</t>
+          <t>470256</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>509414</t>
+          <t>511187</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,53%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A18-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A18-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de que se riesen de él/ella otros/as chicos/as, percibida por el adulto en 2007 (tasa de respuesta: 99,1%)</t>
+          <t>Menores según la frecuencia de que se riesen de él/ella otros/as chicos/as, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 99,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5639</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2698</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10663</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,61%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>5664</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2926</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10311</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2705</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10193</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>4,52%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,22%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5639</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2643</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10435</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6981</t>
+          <t>6591</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17180</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4874</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9243</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3,48%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6,59%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>6862</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>3469</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11883</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3819</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>5,47%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>9,47%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>4874</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>9864</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7480</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18068</t>
+          <t>17897</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5982</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3031</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10646</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4,27%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7,59%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>9533</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5474</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15023</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>5688</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>15798</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>7,6%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,98%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5982</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2912</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9951</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>4,27%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>10127</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21848</t>
+          <t>22898</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22061</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15496</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>29436</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15,74%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11,05%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>16974</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11660</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>24464</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>23971</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>13,53%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,29%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>22061</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>15568</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>30553</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>15,74%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29936</t>
+          <t>31055</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47861</t>
+          <t>49414</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -1174,72 +1174,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>101633</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>92993</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>109808</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>72,5%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>66,33%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>78,33%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>86415</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>78317</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>94036</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>77116</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>94326</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>68,88%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>62,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>74,96%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>101633</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>92549</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>109515</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>72,5%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>176923</t>
+          <t>175040</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>199719</t>
+          <t>199264</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,01%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>140190</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>140190</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>140190</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>125448</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>125448</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>125448</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>140190</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>140190</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>140190</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7095</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3910</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12696</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2618</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7196</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,35%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7095</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3776</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12265</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5698</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15549</t>
+          <t>15505</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6796</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3377</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>11931</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5,85%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>6134</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2781</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>11523</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2774</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>10911</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>3,17%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>6796</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>3325</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>12126</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20290</t>
+          <t>19373</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5355</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2655</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5,23%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>7026</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3865</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>12518</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>3582</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>12342</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>3,63%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,48%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>5355</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2274</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>9924</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>7862</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18218</t>
+          <t>18845</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18129</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25087</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,88%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,29%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>26020</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>18800</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>34474</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>18456</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>34966</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>13,46%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,73%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>17,83%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>18129</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>12873</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>25505</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,88%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34793</t>
+          <t>34599</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54608</t>
+          <t>54888</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -1856,72 +1856,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>166698</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>157473</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>174484</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>81,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77,17%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>85,5%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>151506</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>141329</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>159548</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>140848</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>160471</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>78,38%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>73,11%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>82,54%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>166698</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>157660</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>175392</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>81,69%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>305631</t>
+          <t>304985</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>331286</t>
+          <t>330368</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,14%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>193304</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>193304</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>193304</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12734</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7935</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>19302</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,61%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>8282</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4488</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>13577</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>4615</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>13803</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,6%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>12734</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>7828</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>19351</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15229</t>
+          <t>14530</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>28393</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11670</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>7360</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>18059</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5,25%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>12996</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>8305</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>20079</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>8244</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>19053</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>4,08%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6,3%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>11670</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>7447</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>18748</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18608</t>
+          <t>17470</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33968</t>
+          <t>33786</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>6923</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>17836</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>16559</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>11393</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>23644</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>11362</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>24776</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>5,19%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,57%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>7,42%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>7080</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>17779</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20586</t>
+          <t>20878</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38001</t>
+          <t>36903</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>40189</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>31963</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>51092</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>11,67%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>9,28%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>14,84%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>42993</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>33604</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>52873</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>34055</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>53253</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>13,49%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>10,54%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>16,59%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>40189</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>31399</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>49887</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>11,67%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>70336</t>
+          <t>69781</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>96458</t>
+          <t>97352</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -2538,72 +2538,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>268331</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>255707</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>279764</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>77,94%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>74,28%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>81,26%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>351</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>237921</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>225649</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>250763</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>225457</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>248876</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>74,64%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>70,79%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>78,67%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>268331</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>256237</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>279749</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>77,94%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>487335</t>
+          <t>489274</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>523011</t>
+          <t>523195</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,91%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>344262</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>344262</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>344262</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>473</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>318752</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>318752</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>318752</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>344262</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>344262</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>344262</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de que se riesen de él/ella otros/as chicos/as, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de que se riesen de él/ella otros/as chicos/as, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17742</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12090</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>25189</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,32%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16,08%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>13910</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8543</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20394</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8912</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>20567</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>8,94%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>17742</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>12246</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>25613</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>11,32%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23666</t>
+          <t>24534</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42462</t>
+          <t>42686</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,67%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12883</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7818</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>19883</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>8,22%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4,99%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>12,69%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>14737</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9688</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>21347</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>9634</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>21981</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>9,48%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,23%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>13,73%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12883</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>7910</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>19773</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>8,22%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20558</t>
+          <t>20037</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35971</t>
+          <t>37406</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22136</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15415</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>30330</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>14,13%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>9,84%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>19,36%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>14835</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9721</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>21408</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>9607</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>21875</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>9,54%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,25%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,77%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>22136</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>15523</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>29589</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>14,13%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28525</t>
+          <t>28357</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46663</t>
+          <t>47827</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21002</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>14600</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>29096</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13,4%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>18,57%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>16714</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10897</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>24469</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>11052</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>23555</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>10,75%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>15,73%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>21002</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>14158</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>28291</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>13,4%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29067</t>
+          <t>29409</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49095</t>
+          <t>48606</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -3450,72 +3450,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>82910</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>73215</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>93134</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>52,92%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>46,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>59,44%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>95318</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>86009</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>104548</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>85015</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>105003</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>61,29%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>55,31%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>67,23%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>82910</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>72676</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>92786</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>52,92%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>163824</t>
+          <t>163828</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>194753</t>
+          <t>191188</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>61,24%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3900</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12501</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,16%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>9179</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4982</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14922</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5032</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14731</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,52%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,97%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7161</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3873</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12932</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,1%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23382</t>
+          <t>23416</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17067</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>11277</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>23678</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9,78%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>6,46%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>13,56%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>17026</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11248</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>23888</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>11029</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>24574</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>10,23%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>14,36%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>17067</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>11809</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>24015</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>9,78%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25603</t>
+          <t>26219</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43133</t>
+          <t>45525</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -3911,67 +3911,67 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>10497</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6591</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>17501</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6,01%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10,03%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>11564</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6859</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19213</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>6875</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>17617</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>6,95%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,55%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10497</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>6160</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>16154</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15295</t>
+          <t>16045</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30358</t>
+          <t>30991</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14888</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9566</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21922</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,53%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>21404</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>14950</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>29195</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>14501</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>29532</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>12,86%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,98%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>17,54%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>14888</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9612</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>20933</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,53%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27437</t>
+          <t>27479</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46189</t>
+          <t>46409</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -4132,72 +4132,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>124953</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>114663</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>133586</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>71,58%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>65,68%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>76,52%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>107231</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>97539</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>117232</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>97079</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>117554</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>64,44%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>58,62%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>70,45%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>124953</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>116091</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>134128</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>71,58%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>216347</t>
+          <t>216191</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>245553</t>
+          <t>245580</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174567</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174567</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174567</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166404</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166404</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166404</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174567</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174567</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174567</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>24904</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>17688</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>33895</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,52%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,34%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10,23%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>23089</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>16166</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>31270</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>17105</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>31567</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>7,17%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,71%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>24904</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>17396</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>33433</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>7,52%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38300</t>
+          <t>38796</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59619</t>
+          <t>60325</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -4480,67 +4480,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>29951</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>21750</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>39285</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>9,04%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>6,57%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>11,86%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>31763</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>23699</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>41511</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>23497</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>41166</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>9,87%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7,36%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>12,89%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>29951</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>23042</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>39199</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>9,04%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>49646</t>
+          <t>49775</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>74728</t>
+          <t>75585</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>32633</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>24567</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>42598</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>9,85%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>7,42%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>12,86%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>26398</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>18798</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>35156</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>19584</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>35469</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>8,2%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,92%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>32633</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>24539</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>42357</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>9,85%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>47465</t>
+          <t>48090</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>71949</t>
+          <t>74273</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>35890</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>27659</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>46764</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>10,84%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>8,35%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>14,12%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>38118</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>29172</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>47843</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>28920</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>49124</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>11,84%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>9,06%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>14,86%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>35890</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>27728</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>44694</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>10,84%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>62134</t>
+          <t>62026</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>88881</t>
+          <t>88686</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -4814,72 +4814,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>207863</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>193775</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>223295</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>62,75%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>58,5%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>67,41%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>202550</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>188446</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>216084</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>188135</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>216538</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>62,92%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>58,54%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>67,12%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>207863</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>194452</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>222776</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>62,75%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>389522</t>
+          <t>388297</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>430425</t>
+          <t>429999</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,83%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>331241</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>331241</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>331241</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>457</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>321919</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>321919</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>321919</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>331241</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>331241</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>331241</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de que se riesen de él/ella otros/as chicos/as, percibida por el adulto en 2016 (tasa de respuesta: 98,52%)</t>
+          <t>Menores según la frecuencia de que se riesen de él/ella otros/as chicos/as, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 98,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12251</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7329</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18924</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,61%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,96%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10,21%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>5859</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2663</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11130</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2611</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10837</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,16%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12251</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7743</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>19056</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,61%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12163</t>
+          <t>12187</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25926</t>
+          <t>25887</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10579</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6388</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16725</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5,71%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>9,03%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>12883</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8301</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>20453</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8076</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>18887</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>6,96%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>11,04%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>10579</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5989</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17052</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16767</t>
+          <t>16542</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32082</t>
+          <t>32078</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20522</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>14253</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28907</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11,08%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>7,69%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>15,6%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>13359</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8632</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>20176</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>8337</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>18967</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>7,21%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,9%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>20522</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>14199</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28251</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>11,08%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25457</t>
+          <t>25316</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43323</t>
+          <t>42699</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -5613,72 +5613,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>22179</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16104</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>32823</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11,97%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8,69%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17,72%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>18940</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>12645</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>26525</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>13264</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>27067</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>10,23%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,83%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>14,32%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>22179</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>15581</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>30185</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>11,97%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31768</t>
+          <t>31605</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51873</t>
+          <t>52250</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -5726,72 +5726,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>119728</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>109462</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>130348</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>64,63%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>59,09%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>70,36%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>134142</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>123569</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>144372</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>122944</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>143578</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>72,44%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>66,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>77,96%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>119728</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>108012</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>130503</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>64,63%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>237960</t>
+          <t>238917</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>267760</t>
+          <t>267444</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,2%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>185259</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>185259</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>185259</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>185183</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>185183</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>185183</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>185259</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>185259</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>185259</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5961,67 +5961,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>8725</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4469</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>15117</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,03%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,71%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>7721</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3985</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13175</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4111</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13635</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,52%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8725</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4583</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>15817</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10760</t>
+          <t>11260</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24465</t>
+          <t>25774</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -6074,59 +6074,59 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>14169</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>8636</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>21263</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>8,17%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>12,26%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>13245</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>8113</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>19728</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>8565</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>20577</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>7,76%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4,75%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>11,55%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>14169</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>8691</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>21169</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>5,01%</t>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20273</t>
+          <t>19673</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37549</t>
+          <t>36549</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -6187,67 +6187,67 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>12221</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7310</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18821</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,05%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10,85%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>11944</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>7300</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19260</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>7547</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>19301</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>6,99%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,27%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,28%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>12221</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>7559</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>19427</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>7,05%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17486</t>
+          <t>17225</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33808</t>
+          <t>32931</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>19199</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12703</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>26793</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11,07%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,32%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,45%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>20948</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>14757</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>29773</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>13959</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>29445</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>12,27%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>17,43%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>19199</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>12474</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>26489</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>11,07%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30940</t>
+          <t>30517</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50390</t>
+          <t>51460</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -6408,72 +6408,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>119145</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>108443</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>129407</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>68,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>62,52%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>74,6%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>116930</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>107001</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>126185</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>105151</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>126338</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>68,46%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>62,65%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>73,88%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>119145</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>109588</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>130326</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>68,69%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>221508</t>
+          <t>220717</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>250725</t>
+          <t>250751</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,84%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173460</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173460</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173460</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170789</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170789</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170789</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173460</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173460</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173460</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20976</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13912</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>28738</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5,85%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,88%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,01%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>13581</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8289</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>20649</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>8666</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>21491</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,82%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>20976</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>13792</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>29863</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,85%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25172</t>
+          <t>26559</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44834</t>
+          <t>45545</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>24748</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>17208</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33373</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6,9%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>26128</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>19291</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>35048</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>18663</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>35494</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>7,34%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5,42%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>9,85%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>24748</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>16873</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>33309</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40707</t>
+          <t>40302</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63790</t>
+          <t>62261</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>32743</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>25106</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>43121</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>9,13%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>12,02%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>25302</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>18676</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34537</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>18305</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>33902</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>7,11%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9,7%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>32743</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>24689</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>42366</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>9,13%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>48256</t>
+          <t>45675</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>72384</t>
+          <t>71557</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>41379</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>32892</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>52903</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>11,54%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>14,75%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>39889</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>30920</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>50458</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>31188</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>51363</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>11,21%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>8,69%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>14,17%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>41379</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>32854</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>54111</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>11,54%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66607</t>
+          <t>67737</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>94505</t>
+          <t>96216</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -7090,72 +7090,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>238874</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>221335</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>252131</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>66,59%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>61,7%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>70,29%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>359</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>251072</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>235151</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>263536</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>237275</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>264516</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>70,53%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>66,06%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>74,03%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>238874</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>223033</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>252592</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>66,59%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>470256</t>
+          <t>469851</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>511187</t>
+          <t>511129</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,52%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>358719</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>358719</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>358719</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>355972</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>355972</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>355972</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>492</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>358719</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>358719</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>358719</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
